--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/magallanes.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/magallanes.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M84"/>
+  <dimension ref="A1:M90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -605,7 +605,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2039,7 +2039,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1096-63-CM25</t>
+          <t>874750-208-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>BLOOMBERRY COMERCIAL SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.330.742-5</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>23370.74</v>
+        <v>2183.95</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>874750-208-CM25</t>
+          <t>1096-63-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>BLOOMBERRY COMERCIAL SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>76.330.742-5</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>2183.95</v>
+        <v>23370.74</v>
       </c>
     </row>
     <row r="29">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE PUERTO WILLIAMS</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (M)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (M)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4662,7 +4662,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1000813-47-CM26</t>
+          <t>1000813-45-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. del Campo Militar Austral</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>1660.63</v>
+        <v>2066.65</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1000813-45-CM26</t>
+          <t>1000813-46-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. del Campo Militar Austral</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>2066.65</v>
+        <v>2199.88</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1000813-46-CM26</t>
+          <t>1000813-47-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. del Campo Militar Austral</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>2199.88</v>
+        <v>1660.63</v>
       </c>
     </row>
     <row r="73">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. del Campo Militar Austral</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. del Campo Militar Austral</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. del Campo Militar Austral</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. del Campo Militar Austral</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5572,6 +5572,372 @@
       </c>
       <c r="M84" s="2" t="n">
         <v>788.51</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>1000813-351-CM26</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>61.999.040-4</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>COMERCIAL E INVERSIONES CROSUR LTDA</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>78.197.550-8</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>5336.31</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>1109692-244-CM26</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>62.000.760-9</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES Y ANTARTICA CHILENA</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>JAIME GONZALO URIBE HERMOSILLA</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>12.364.273-2</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>1031.68</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2661-33-CM26</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>69.250.100-4</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>1447.97</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>1000813-368-CM26</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>61.999.040-4</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>COMERCIAL E INVERSIONES CROSUR LTDA</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>78.197.550-8</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>1052.13</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>874750-337-CM26</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>61.607.903-4</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>COMERCIAL GRAN VIA SPA</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>3740.06</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>1000813-372-CM26</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>61.999.040-4</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>COMERCIAL E INVERSIONES CROSUR LTDA</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>78.197.550-8</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>12595.42</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/magallanes.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/magallanes.xlsx
@@ -562,7 +562,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +749,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +936,11 @@
           <t>76.193.188-1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1062,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1432,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2900,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +2965,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3274,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3705,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +3892,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4445,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4510,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4697,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5067,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5620,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +5929,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/magallanes.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/magallanes.xlsx
@@ -875,7 +875,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/magallanes.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/magallanes.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M90"/>
+  <dimension ref="A1:M93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2986,7 +2986,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1038-242-CM25</t>
+          <t>4305-138-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3011,12 +3011,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.943.400-5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3026,12 +3026,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>COMERCIAL E INVERSIONES CROSUR LTDA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>78.197.550-8</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3041,13 +3041,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>800.41</v>
+        <v>1996.62</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>4305-138-CM25</t>
+          <t>1038-242-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.943.400-5</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>COMERCIAL E INVERSIONES CROSUR LTDA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>78.197.550-8</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3102,7 +3102,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>1996.62</v>
+        <v>800.41</v>
       </c>
     </row>
     <row r="44">
@@ -4718,7 +4718,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1000813-45-CM26</t>
+          <t>1000813-46-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4773,13 +4773,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>2066.65</v>
+        <v>2199.88</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1000813-46-CM26</t>
+          <t>1000813-47-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4834,13 +4834,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>2199.88</v>
+        <v>1660.63</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1000813-47-CM26</t>
+          <t>1000813-45-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4895,13 +4895,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>1660.63</v>
+        <v>2066.65</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1070-34-CM26</t>
+          <t>1070-35-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4956,13 +4956,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>36442.47</v>
+        <v>47453.27</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1070-35-CM26</t>
+          <t>1070-34-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5017,7 +5017,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>47453.27</v>
+        <v>36442.47</v>
       </c>
     </row>
     <row r="75">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -6006,6 +6006,189 @@
       </c>
       <c r="M90" s="2" t="n">
         <v>12595.42</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>1070-209-CM26</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>LUIS ALEXANDER</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>76.962.756-1</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>77115.28999999999</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>1490610-11-CM26</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>61.981.340-5</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>JAIME GONZALO URIBE HERMOSILLA</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>12.364.273-2</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>9388.940000000001</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>3704-337-CM26</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>69.254.400-5</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>2164.88</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/magallanes.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/magallanes.xlsx
@@ -609,7 +609,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
